--- a/Result/profitability/8066.xlsx
+++ b/Result/profitability/8066.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.86</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6950000000000001</v>
+        <v>-0.67375</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.9725</v>
+        <v>-22.34125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.68</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.855</v>
+        <v>-0.895</v>
       </c>
       <c r="N3" t="n">
-        <v>-67.37625</v>
+        <v>-67.56</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.01</v>
+        <v>-1.06375</v>
       </c>
       <c r="N4" t="n">
-        <v>-99.11125</v>
+        <v>-99.53500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1325</v>
+        <v>-0.99</v>
       </c>
       <c r="N5" t="n">
-        <v>-339.635</v>
+        <v>-339.33</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.02375</v>
+        <v>-0.90625</v>
       </c>
       <c r="N6" t="n">
-        <v>-766.6612499999999</v>
+        <v>-766.7449999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.92125</v>
+        <v>-0.8075</v>
       </c>
       <c r="N7" t="n">
-        <v>-1277.09625</v>
+        <v>-1277.2825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.83125</v>
+        <v>-0.74625</v>
       </c>
       <c r="N8" t="n">
-        <v>-1688.13875</v>
+        <v>-1687.90875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.755</v>
+        <v>-0.7549999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>-2585.39625</v>
@@ -9808,6 +9808,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1187</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1072</v>
+      </c>
+      <c r="E75" t="n">
+        <v>115</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.6162500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.39125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7472527472527473</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2346938775510203</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8321167883211679</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3370165745856353</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
